--- a/data/trans_dic/IP13_R1_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP13_R1_2023-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolor</t>
+          <t>Menores que limitaron su actividad por dolor (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -538,7 +539,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -571,24 +572,24 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,96</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -621,24 +622,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,25</t>
+          <t>0,0; 3,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 8,52</t>
+          <t>1,58; 8,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,89; 4,88</t>
+          <t>0,93; 4,7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,44</t>
+          <t>0,0; 8,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,21</t>
+          <t>0,0; 5,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,93</t>
+          <t>0,44; 4,61</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,93</t>
+          <t>0,0; 6,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,99</t>
+          <t>0,0; 7,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,38</t>
+          <t>0,0; 4,32</t>
         </is>
       </c>
     </row>
@@ -771,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,14</t>
+          <t>0,0; 7,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,72</t>
+          <t>0,0; 4,38</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -821,24 +822,24 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,12; 10,28</t>
+          <t>1,17; 12,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,93</t>
+          <t>0,0; 3,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,62; 5,23</t>
+          <t>0,53; 5,28</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,83; 7,91</t>
+          <t>1,78; 7,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,85</t>
+          <t>0,5; 4,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,53; 5,09</t>
+          <t>1,44; 5,0</t>
         </is>
       </c>
     </row>
@@ -921,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,07</t>
+          <t>0,0; 1,97</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,2</t>
+          <t>0,0; 2,76</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,98</t>
+          <t>0,0; 1,63</t>
         </is>
       </c>
     </row>
@@ -971,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,68</t>
+          <t>0,89; 2,53</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,57</t>
+          <t>0,9; 2,5</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,07; 2,26</t>
+          <t>1,03; 2,17</t>
         </is>
       </c>
     </row>
@@ -1007,4 +1008,750 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que limitaron su actividad por dolor (tasa de respuesta: 99,95%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>815</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4952</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5767</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5046</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2014; 10313</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2367; 11957</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1374</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1098</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2473</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4715</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3396</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>554; 5786</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>948</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>968</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1916</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4640</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5529</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 6403</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1043</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1043</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3225</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3293</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>1916</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2274</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>539; 5945</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2032</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>538; 5408</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>5082</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>2577</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>7658</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>2215; 9667</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>774; 6911</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>4022; 13994</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>868</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>1312</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>0; 2590</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4327</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4703</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>10579</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>11864</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>22443</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>5914; 16840</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>6848; 19006</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>14731; 31003</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP13_R1_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP13_R1_2023-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolor (tasa de respuesta: 99,95%)</t>
+          <t>Menores que en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por dolor (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,98</t>
+          <t>0,0; 3,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,58; 8,08</t>
+          <t>1,53; 9,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,7</t>
+          <t>0,87; 4,54</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,09</t>
+          <t>0,0; 7,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,06</t>
+          <t>0,0; 5,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,61</t>
+          <t>0,52; 4,73</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,62</t>
+          <t>0,0; 6,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,08</t>
+          <t>0,0; 6,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,32</t>
+          <t>0,0; 4,12</t>
         </is>
       </c>
     </row>
@@ -777,12 +777,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,92</t>
+          <t>0,0; 9,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,38</t>
+          <t>0,0; 4,97</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,17; 12,88</t>
+          <t>1,17; 11,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,62</t>
+          <t>0,0; 3,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,53; 5,28</t>
+          <t>0,62; 5,46</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,78; 7,76</t>
+          <t>1,77; 8,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,45</t>
+          <t>0,51; 4,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,44; 5,0</t>
+          <t>1,39; 4,83</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,97</t>
+          <t>0,0; 1,7</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,76</t>
+          <t>0,0; 3,39</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,63</t>
+          <t>0,0; 1,68</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,53</t>
+          <t>0,9; 2,55</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,5</t>
+          <t>0,89; 2,6</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,17</t>
+          <t>1,09; 2,22</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolor (tasa de respuesta: 99,95%)</t>
+          <t>Menores que en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por dolor (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5046</t>
+          <t>0; 4174</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2014; 10313</t>
+          <t>1952; 11865</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2367; 11957</t>
+          <t>2208; 11540</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4715</t>
+          <t>0; 4564</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3396</t>
+          <t>0; 3765</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>554; 5786</t>
+          <t>654; 5929</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4640</t>
+          <t>0; 4633</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5529</t>
+          <t>0; 5229</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 6403</t>
+          <t>0; 6115</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3225</t>
+          <t>0; 4040</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3293</t>
+          <t>0; 3735</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>539; 5945</t>
+          <t>538; 5307</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 2032</t>
+          <t>0; 1810</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>538; 5408</t>
+          <t>635; 5590</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2215; 9667</t>
+          <t>2203; 10168</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>774; 6911</t>
+          <t>796; 7390</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4022; 13994</t>
+          <t>3903; 13522</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 2590</t>
+          <t>0; 2238</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 4327</t>
+          <t>0; 5315</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 4703</t>
+          <t>0; 4847</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>5914; 16840</t>
+          <t>5973; 16943</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>6848; 19006</t>
+          <t>6812; 19822</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>14731; 31003</t>
+          <t>15480; 31705</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP13_R1_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP13_R1_2023-Provincia-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,29</t>
+          <t>1,3; 8,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 9,3</t>
+          <t>0,0; 3,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,87; 4,54</t>
+          <t>1,02; 5,33</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,83</t>
+          <t>0,0; 5,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,61</t>
+          <t>0,0; 8,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,73</t>
+          <t>0,55; 4,88</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,61</t>
+          <t>0,0; 7,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,69</t>
+          <t>0,0; 7,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,12</t>
+          <t>0,0; 4,73</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0,0; 9,25</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 9,92</t>
-        </is>
-      </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,97</t>
+          <t>0,0; 4,94</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,17; 11,5</t>
+          <t>0,0; 3,31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,22</t>
+          <t>1,29; 10,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,62; 5,46</t>
+          <t>0,67; 5,81</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,77; 8,17</t>
+          <t>0,6; 5,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,76</t>
+          <t>1,79; 8,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,39; 4,83</t>
+          <t>1,58; 5,56</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0,0; 3,41</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>0,0; 1,7</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,39</t>
-        </is>
-      </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,68</t>
+          <t>0,0; 1,93</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,55</t>
+          <t>0,92; 2,72</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,6</t>
+          <t>0,99; 2,85</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,22</t>
+          <t>1,12; 2,38</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>4568</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4952</t>
+          <t>690</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5767</t>
+          <t>5257</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4174</t>
+          <t>1506; 10173</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1952; 11865</t>
+          <t>0; 3360</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2208; 11540</t>
+          <t>2210; 11533</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1374</t>
+          <t>910</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1098</t>
+          <t>1338</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2473</t>
+          <t>2249</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4564</t>
+          <t>0; 3093</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3765</t>
+          <t>0; 4766</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>654; 5929</t>
+          <t>635; 5658</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>979</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>987</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1916</t>
+          <t>1966</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4633</t>
+          <t>0; 5746</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5229</t>
+          <t>0; 5054</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 6115</t>
+          <t>0; 6761</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1083</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>1043</t>
-        </is>
-      </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1083</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>0; 3663</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>0; 4040</t>
-        </is>
-      </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3735</t>
+          <t>0; 3714</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1916</t>
+          <t>248</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>2041</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2274</t>
+          <t>2290</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>538; 5307</t>
+          <t>0; 1619</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 1810</t>
+          <t>588; 5021</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>635; 5590</t>
+          <t>636; 5505</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>5082</t>
+          <t>2660</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2577</t>
+          <t>5096</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7658</t>
+          <t>7757</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2203; 10168</t>
+          <t>847; 7977</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>796; 7390</t>
+          <t>2191; 10082</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3903; 13522</t>
+          <t>4163; 14655</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>950</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>385</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1312</t>
+          <t>1334</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 2238</t>
+          <t>0; 5436</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 5315</t>
+          <t>0; 2385</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 4847</t>
+          <t>0; 5790</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>10579</t>
+          <t>11398</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>11864</t>
+          <t>10538</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>22443</t>
+          <t>21936</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>5973; 16943</t>
+          <t>6463; 19047</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>6812; 19822</t>
+          <t>6234; 17946</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>15480; 31705</t>
+          <t>14947; 31695</t>
         </is>
       </c>
     </row>
